--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261026억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 262360억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261074억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258876억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 256251억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250335억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245670억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -918,7 +918,7 @@
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 93억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
@@ -1767,49 +1767,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261026억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 262360억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261074억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258876억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 256251억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250335억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245670억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2240,7 +2240,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 93억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6476,26 +6476,26 @@
         <v>0.499576</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.280345</v>
+        <v>0.284355</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08608</v>
+        <v>0.08942</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.016969</v>
+        <v>0.020059</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.018296</v>
+        <v>-0.015337</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.031961</v>
+        <v>-0.03533</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.041079</v>
+        <v>-0.044366</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.05101</v>
+        <v>-0.054183</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6625,29 +6625,29 @@
         <v>0.147153</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.147158</v>
+        <v>0.147161</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.147142</v>
+        <v>0.147154</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.147131</v>
+        <v>0.14716</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.147128</v>
+        <v>0.147176</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.147163</v>
+        <v>0.147156</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.147153</v>
+        <v>0.147146</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.147127</v>
+        <v>0.147173</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6780,29 +6780,29 @@
         <v>-0.010567</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010557</v>
+        <v>-0.010582</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.01056</v>
+        <v>-0.010585</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010548</v>
+        <v>-0.010575</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010579</v>
+        <v>-0.010548</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010546</v>
+        <v>-0.01055</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010589</v>
+        <v>-0.010593</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010549</v>
+        <v>-0.010553</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7073,7 +7073,7 @@
         <v>2.16</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AN25" s="29" t="n">
         <v>2.16</v>
@@ -7522,7 +7522,7 @@
         <v>0.152174</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.155556</v>
+        <v>0.159091</v>
       </c>
       <c r="AI28" s="24" t="n">
         <v>0.16</v>
@@ -7532,7 +7532,7 @@
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.157895</v>
+        <v>0.160714</v>
       </c>
       <c r="AL28" s="24" t="n">
         <v>0.150943</v>
@@ -7674,20 +7674,20 @@
         <v>1</v>
       </c>
       <c r="AG29" s="24" t="n">
+        <v>0.974359</v>
+      </c>
+      <c r="AH29" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AH29" s="24" t="n">
-        <v>0.973684</v>
-      </c>
       <c r="AI29" s="24" t="n">
-        <v>1</v>
+        <v>0.97619</v>
       </c>
       <c r="AJ29" s="25">
         <f>IFERROR(subQ!AJ17/subQ!AJ16,"")</f>
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.979167</v>
+        <v>1</v>
       </c>
       <c r="AL29" s="24" t="n">
         <v>0.977778</v>
@@ -7936,26 +7936,26 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>1.26</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8192,26 +8192,26 @@
         <v>0.004703</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.00915</v>
+        <v>-0.009256</v>
       </c>
       <c r="AH33" s="24" t="n">
         <v>0.003973</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.004599</v>
+        <v>0.004492</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.005004</v>
+        <v>0.005111</v>
       </c>
       <c r="AL33" s="24" t="n">
         <v>-0.008581</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.004808</v>
+        <v>0.004702</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.005423</v>
+        <v>0.005531</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8850,26 +8850,26 @@
         <v>0.005504</v>
       </c>
       <c r="AG39" s="24" t="n">
-        <v>8.883139999999999</v>
+        <v>8.954950999999999</v>
       </c>
       <c r="AH39" s="24" t="n">
-        <v>10.336066</v>
+        <v>10.512054</v>
       </c>
       <c r="AI39" s="24" t="n">
-        <v>5.465204</v>
+        <v>5.567019</v>
       </c>
       <c r="AJ39" s="25" t="n"/>
       <c r="AK39" s="24" t="n">
-        <v>5.385605</v>
+        <v>5.534209</v>
       </c>
       <c r="AL39" s="24" t="n">
-        <v>0.022069</v>
+        <v>0.02984</v>
       </c>
       <c r="AM39" s="24" t="n">
-        <v>-0.07090299999999999</v>
+        <v>-0.078573</v>
       </c>
       <c r="AN39" s="24" t="n">
-        <v>-0.128372</v>
+        <v>-0.136071</v>
       </c>
       <c r="AO39" s="25" t="n"/>
     </row>
@@ -9273,29 +9273,29 @@
         <v>-0.010567</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.010557</v>
+        <v>-0.010582</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.01056</v>
+        <v>-0.010585</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.010548</v>
+        <v>-0.010575</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ33/subQ!AJ32,"")</f>
         <v/>
       </c>
       <c r="AK42" s="24" t="n">
-        <v>-0.010579</v>
+        <v>-0.010548</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.010546</v>
+        <v>-0.01055</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.010589</v>
+        <v>-0.010593</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.010549</v>
+        <v>-0.010553</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO33/subQ!AO32,"")</f>
@@ -32684,7 +32684,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="30">
@@ -32704,7 +32704,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>221.58</v>
+        <v>223.19</v>
       </c>
     </row>
     <row r="32">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254552억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255541억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265726억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 275679억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 287258억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 302650억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 320867억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 340383억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 359701억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 376820억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,7 +924,7 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 93억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
@@ -936,13 +936,13 @@
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 92억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 92억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1546,18 +1546,6 @@
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AM39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AN39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ TTM EPS(추정 포함)</t>
@@ -1761,55 +1749,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254552억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255541억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265726억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275679억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 287258억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 302650억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 320867억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 340383억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 359701억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 376820억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2246,25 +2234,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
+        <t>추정: 이자손익 = 이자발생자산 93억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AL11" authorId="0" shapeId="0">
+      <text>
         <t>추정: 이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
-    <comment ref="AL11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+    <comment ref="AM11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 92억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
-    <comment ref="AM11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 94억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 92억 × 9.17% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -3494,18 +3482,6 @@
       </text>
     </comment>
     <comment ref="AL30" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AM30" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AN30" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
 [yoy]</t>
@@ -4290,7 +4266,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4394,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.8, "op_wape_pct": 150.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 107.47, "rev_act": 124.33, "op_pred": -4.3, "op_act": 1.52}, {"q": "2025Q4", "rev_pred": 95.29, "rev_act": 128.52, "op_pred": -3.81, "op_act": 2.9}, {"q": "2026Q1", "rev_pred": 95.09, "rev_act": 110.44, "op_pred": -3.8, "op_act": -3.69}, {"q": "2026Q2", "rev_pred": 111.26, "rev_act": 134.65, "op_pred": -4.45, "op_act": 9.63}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.8, "op_wape_pct": 150.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 107.47, "rev_act": 124.33, "op_pred": -4.3, "op_act": 1.52}, {"q": "2025Q4", "rev_pred": 95.29, "rev_act": 128.52, "op_pred": -3.81, "op_act": 2.9}, {"q": "2026Q1", "rev_pred": 95.09, "rev_act": 110.44, "op_pred": -3.8, "op_act": -3.69}, {"q": "2026Q2", "rev_pred": 111.26, "rev_act": 134.65, "op_pred": -4.45, "op_act": 9.63}]}</t>
         </is>
       </c>
     </row>
@@ -6469,33 +6445,33 @@
         <v>0.276411</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.283945</v>
+        <v>0.288925</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.499576</v>
+        <v>0.526559</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284355</v>
+        <v>0.345328</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08942</v>
+        <v>0.195034</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020059</v>
+        <v>0.184365</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.015337</v>
+        <v>0.207545</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.03533</v>
+        <v>0.234723</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.044366</v>
+        <v>0.252215</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.054183</v>
+        <v>0.245069</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6615,39 +6591,39 @@
         <v>0.147142</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.147143</v>
+        <v>0.147178</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
+        <v>0.147162</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>0.147171</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>0.147174</v>
+      </c>
+      <c r="AI22" s="24" t="n">
         <v>0.147153</v>
-      </c>
-      <c r="AG22" s="24" t="n">
-        <v>0.147161</v>
-      </c>
-      <c r="AH22" s="24" t="n">
-        <v>0.147154</v>
-      </c>
-      <c r="AI22" s="24" t="n">
-        <v>0.14716</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.147176</v>
+        <v>0.147166</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.147156</v>
+        <v>0.147136</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.147146</v>
+        <v>0.147134</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.147173</v>
+        <v>0.147132</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6770,39 +6746,39 @@
         <v>-0.010587</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010545</v>
+        <v>-0.010564</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010567</v>
+        <v>-0.010558</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010582</v>
+        <v>-0.010544</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010585</v>
+        <v>-0.010546</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010575</v>
+        <v>-0.010551</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010548</v>
+        <v>-0.010561</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.01055</v>
+        <v>-0.010551</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010593</v>
+        <v>-0.01057</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010553</v>
+        <v>-0.010562</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7067,16 +7043,16 @@
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7516,32 +7492,32 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.150943</v>
+        <v>0.163265</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.152174</v>
+        <v>0.162162</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.159091</v>
+        <v>0.153846</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.160714</v>
+        <v>0.166667</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.150943</v>
+        <v>-0</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.150943</v>
+        <v>-0</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.15</v>
+        <v>-0</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -7664,23 +7640,23 @@
         <v>0.979592</v>
       </c>
       <c r="AD29" s="24" t="n">
-        <v>1</v>
+        <v>0.9772729999999999</v>
       </c>
       <c r="AE29" s="25">
         <f>IFERROR(subQ!AE17/subQ!AE16,"")</f>
         <v/>
       </c>
       <c r="AF29" s="24" t="n">
+        <v>0.97619</v>
+      </c>
+      <c r="AG29" s="24" t="n">
         <v>1</v>
-      </c>
-      <c r="AG29" s="24" t="n">
-        <v>0.974359</v>
       </c>
       <c r="AH29" s="24" t="n">
         <v>1</v>
       </c>
       <c r="AI29" s="24" t="n">
-        <v>0.97619</v>
+        <v>0.941176</v>
       </c>
       <c r="AJ29" s="25">
         <f>IFERROR(subQ!AJ17/subQ!AJ16,"")</f>
@@ -7690,10 +7666,10 @@
         <v>1</v>
       </c>
       <c r="AL29" s="24" t="n">
-        <v>0.977778</v>
+        <v>1</v>
       </c>
       <c r="AM29" s="24" t="n">
-        <v>0.977778</v>
+        <v>0.962963</v>
       </c>
       <c r="AN29" s="24" t="n">
         <v>1</v>
@@ -7929,7 +7905,7 @@
         <v>-0.0005</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
@@ -7942,20 +7918,20 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>1.26</v>
       </c>
       <c r="AM31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN31" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8061,23 +8037,23 @@
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
         <v>1.26</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -8185,33 +8161,33 @@
         <v>0.005298</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.004726</v>
+        <v>0.004618</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.004703</v>
+        <v>0.00449</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.009256</v>
+        <v>-0.010111</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.003973</v>
+        <v>0.002365</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.004492</v>
+        <v>0.001823</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.005111</v>
+        <v>0.001071</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.008581</v>
+        <v>-0.014439</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.004702</v>
+        <v>-0.002821</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.005531</v>
+        <v>-0.003809</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8843,34 +8819,30 @@
         <v>-0.793632</v>
       </c>
       <c r="AD39" s="24" t="n">
-        <v>-0.116718</v>
+        <v>-0.115762</v>
       </c>
       <c r="AE39" s="25" t="n"/>
       <c r="AF39" s="24" t="n">
-        <v>0.005504</v>
+        <v>0.009081000000000001</v>
       </c>
       <c r="AG39" s="24" t="n">
-        <v>8.954950999999999</v>
+        <v>9.567351</v>
       </c>
       <c r="AH39" s="24" t="n">
-        <v>10.512054</v>
+        <v>12.624397</v>
       </c>
       <c r="AI39" s="24" t="n">
-        <v>5.567019</v>
+        <v>8.467136</v>
       </c>
       <c r="AJ39" s="25" t="n"/>
       <c r="AK39" s="24" t="n">
-        <v>5.534209</v>
+        <v>12.332152</v>
       </c>
       <c r="AL39" s="24" t="n">
-        <v>0.02984</v>
-      </c>
-      <c r="AM39" s="24" t="n">
-        <v>-0.078573</v>
-      </c>
-      <c r="AN39" s="24" t="n">
-        <v>-0.136071</v>
-      </c>
+        <v>3.19361</v>
+      </c>
+      <c r="AM39" s="31" t="n"/>
+      <c r="AN39" s="31" t="n"/>
       <c r="AO39" s="25" t="n"/>
     </row>
     <row r="40">
@@ -9263,39 +9235,39 @@
         <v>-0.010587</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.010545</v>
+        <v>-0.010564</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE33/subQ!AE32,"")</f>
         <v/>
       </c>
       <c r="AF42" s="24" t="n">
-        <v>-0.010567</v>
+        <v>-0.010558</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.010582</v>
+        <v>-0.010544</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.010585</v>
+        <v>-0.010546</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.010575</v>
+        <v>-0.010551</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ33/subQ!AJ32,"")</f>
         <v/>
       </c>
       <c r="AK42" s="24" t="n">
-        <v>-0.010548</v>
+        <v>-0.010561</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.01055</v>
+        <v>-0.010551</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.010593</v>
+        <v>-0.01057</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.010553</v>
+        <v>-0.010562</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO33/subQ!AO32,"")</f>
@@ -10038,7 +10010,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13529,7 +13501,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24752,14 +24724,8 @@
         <f>IFERROR(AG30*(1+변수!AL39),"")</f>
         <v/>
       </c>
-      <c r="AM30" s="20">
-        <f>IFERROR(AH30*(1+변수!AM39),"")</f>
-        <v/>
-      </c>
-      <c r="AN30" s="20">
-        <f>IFERROR(AI30*(1+변수!AN39),"")</f>
-        <v/>
-      </c>
+      <c r="AM30" s="20" t="n"/>
+      <c r="AN30" s="20" t="n"/>
       <c r="AO30" s="35">
         <f>SUM(AK30:AN30)</f>
         <v/>
@@ -32684,7 +32650,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -32704,7 +32670,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>223.19</v>
+        <v>236.92</v>
       </c>
     </row>
     <row r="32">
@@ -32724,7 +32690,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253980억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263158억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 272093억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283204억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298569억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316779억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336299억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355620억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372744억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253980억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263158억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 272093억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283204억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298569억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316779억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336299억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355620억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372744억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>· 판관비율 14.72% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
+          <t>· 판관비율 14.71% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 7.59% / 부채 0.36% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0745, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": null}</t>
+          <t>· 이자율 자산 7.45% / 부채 0.00% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0745, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": null}</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3295</v>
+        <v>3310</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5900,7 +5900,7 @@
         <v>3640</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>3380</v>
+        <v>3400</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3280</v>
+        <v>3290</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6237,33 +6237,33 @@
         <v>0.273434509</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.281065687</v>
+        <v>0.280987877</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.511799844</v>
+        <v>0.511618747</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.327875281</v>
+        <v>0.327578217</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180899444</v>
+        <v>0.180646791</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175595238</v>
+        <v>0.175362935</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203821275</v>
+        <v>0.203665988</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235961969</v>
+        <v>0.235958827</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255723149</v>
+        <v>0.255777873</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248411263</v>
+        <v>0.248527132</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6548,39 +6548,39 @@
         <v>-0.010548257</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010568513</v>
+        <v>-0.010569155</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010541447</v>
+        <v>-0.01054271</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.01057047</v>
+        <v>-0.010572835</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010590501</v>
+        <v>-0.010592767</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010591578</v>
+        <v>-0.010594315</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010547788</v>
+        <v>-0.010550413</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010588714</v>
+        <v>-0.010591111</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.01056353</v>
+        <v>-0.01056533</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010553325</v>
+        <v>-0.010555073</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.004569124</v>
+        <v>0.005142219</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000439623</v>
+        <v>6.6889e-05</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.004616004</v>
+        <v>-0.00415971</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.257929246</v>
+        <v>1.258341296</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.006235505</v>
+        <v>-0.005325015</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.007183778</v>
+        <v>-0.006255905</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.000540024</v>
+        <v>0.001509791</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.25674635</v>
+        <v>1.257785938</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.00512057</v>
+        <v>-0.003307459</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.003688101</v>
+        <v>0.005521031</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.001506959</v>
+        <v>0.002072257</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002746566</v>
+        <v>-0.002246946</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003269927</v>
+        <v>0.003720014</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.257277147</v>
+        <v>1.257683591</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005470396</v>
+        <v>-0.004572294</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005453386</v>
+        <v>-0.004538137</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003253765</v>
+        <v>-0.005789662</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.252504904</v>
+        <v>1.263530346</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.007023692</v>
+        <v>-0.005235248</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.002889623</v>
+        <v>0.004697616</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7857,13 +7857,13 @@
         <v>-0.003756574</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031674208</v>
+        <v>-0.031485671</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.011487539</v>
+        <v>-0.011679969</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.013393736</v>
+        <v>-0.01319677</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7985,13 +7985,13 @@
         <v>-0.00207857</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.017496355</v>
+        <v>-0.01739221</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006253975</v>
+        <v>-0.0063593</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.007253333</v>
+        <v>-0.007146667</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3295</v>
+        <v>3310</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471598523318323</v>
+        <v>0.1471495991824452</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07587354845034724</v>
+        <v>0.07447556767579602</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.003634272242930141</v>
+        <v>0</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18887,7 +18887,7 @@
         <v>-20.06</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V64" s="18" t="n">
         <v>-1.58</v>
@@ -18964,7 +18964,7 @@
         <v>-20.06</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V65" s="18" t="n">
         <v>-1.58</v>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>701.0599999999999</v>
+        <v>704.26</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3310</v>
+        <v>3260</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3290</v>
+        <v>3288.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6237,33 +6237,33 @@
         <v>0.273434509</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.280987877</v>
+        <v>0.280910067</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.511618747</v>
+        <v>0.51143765</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.327578217</v>
+        <v>0.327281153</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180646791</v>
+        <v>0.180330975</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175362935</v>
+        <v>0.175069858</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203665988</v>
+        <v>0.203510664</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235958827</v>
+        <v>0.235955685</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255777873</v>
+        <v>0.25584631</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248527132</v>
+        <v>0.248655914</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6548,39 +6548,39 @@
         <v>-0.010548257</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010569155</v>
+        <v>-0.010569797</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.01054271</v>
+        <v>-0.010543973</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010572835</v>
+        <v>-0.010575201</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010592767</v>
+        <v>-0.010595601</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010594315</v>
+        <v>-0.010545906</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010550413</v>
+        <v>-0.010553039</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010591111</v>
+        <v>-0.010548237</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.01056533</v>
+        <v>-0.010567581</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010555073</v>
+        <v>-0.010557258</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.005142219</v>
+        <v>0.005126805</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>6.6889e-05</v>
+        <v>-0.009948557</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.00415971</v>
+        <v>0.005824842</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.258341296</v>
+        <v>1.258325847</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005325015</v>
+        <v>-0.005343082</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006255905</v>
+        <v>0.003725885</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001509791</v>
+        <v>0.00149169</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257785938</v>
+        <v>1.257767885</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.003307459</v>
+        <v>0.006674811</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.005521031</v>
+        <v>-0.004310413</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.002072257</v>
+        <v>0.002057053</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002246946</v>
+        <v>-0.002262182</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003720014</v>
+        <v>0.003704775</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.257683591</v>
+        <v>1.257668353</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004572294</v>
+        <v>-0.004590115</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004538137</v>
+        <v>-0.004692154</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005789662</v>
+        <v>0.004192484</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.263530346</v>
+        <v>1.263376484</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005235248</v>
+        <v>0.004747263</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.004697616</v>
+        <v>0.004863878</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7860,10 +7860,10 @@
         <v>-0.031485671</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.011679969</v>
+        <v>-0.011485303</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.01319677</v>
+        <v>-0.013391099</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7988,10 +7988,10 @@
         <v>-0.01739221</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.0063593</v>
+        <v>-0.006253312</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.007146667</v>
+        <v>-0.00725256</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3310</v>
+        <v>3260</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,255원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,280원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471495991824452</v>
+        <v>0.1471475019133079</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07447556767579602</v>
+        <v>0.07447481591712297</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>704.26</v>
+        <v>693.62</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3260</v>
+        <v>3250</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5991,7 +5991,7 @@
         <v>2505</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3125</v>
+        <v>3100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3288.8</v>
+        <v>3282</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6241,26 +6241,26 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.51143765</v>
+        <v>0.511347101</v>
       </c>
       <c r="AG21" s="24" t="n">
         <v>0.327281153</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180330975</v>
+        <v>0.180267812</v>
       </c>
       <c r="AI21" s="24" t="n">
         <v>0.175069858</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203510664</v>
+        <v>0.203582769</v>
       </c>
       <c r="AL21" s="24" t="n">
         <v>0.235955685</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.25584631</v>
+        <v>0.255913518</v>
       </c>
       <c r="AN21" s="24" t="n">
         <v>0.248655914</v>
@@ -6555,13 +6555,13 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010543973</v>
+        <v>-0.010544605</v>
       </c>
       <c r="AG23" s="24" t="n">
         <v>-0.010575201</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010595601</v>
+        <v>-0.010596168</v>
       </c>
       <c r="AI23" s="24" t="n">
         <v>-0.010545906</v>
@@ -7457,23 +7457,23 @@
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.005824842</v>
+        <v>0.005824802</v>
       </c>
       <c r="AG29" s="30" t="n">
         <v>1.258325847</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005343082</v>
+        <v>-0.005343076</v>
       </c>
       <c r="AI29" s="30" t="n">
         <v>0.003725885</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.00149169</v>
+        <v>0.001491692</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257767885</v>
+        <v>1.257767884</v>
       </c>
       <c r="AM29" s="30" t="n">
         <v>0.006674811</v>
@@ -7585,26 +7585,26 @@
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003704775</v>
+        <v>0.003704736</v>
       </c>
       <c r="AG30" s="30" t="n">
         <v>1.257668353</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004590115</v>
+        <v>-0.004590109</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004692154</v>
+        <v>-0.004692155</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.004192484</v>
+        <v>0.004192485</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.263376484</v>
+        <v>1.263376485</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004747263</v>
+        <v>0.004747262</v>
       </c>
       <c r="AN30" s="30" t="n">
         <v>0.004863878</v>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3260</v>
+        <v>3250</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,280원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471475019133079</v>
+        <v>0.1471490135448181</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>693.62</v>
+        <v>691.49</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239810억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 240366억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1584,61 +1584,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239810억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 240366억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4098,14 +4098,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 15.49% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 15.50% · 근거: 최근 12분기 유효세율 15.5%(5~27% 안 — 그대로)</t>
+          <t>· 세율 16.42% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 15.50% · 근거: 최근 12분기 유효세율 15.5%(5~27% 안 — 그대로)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>· 판관비율 14.71% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
+          <t>· 판관비율 14.72% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -6234,36 +6234,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.273434509</v>
+        <v>0.276330141</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.280910067</v>
+        <v>0.287368306</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.511347101</v>
+        <v>0.520039769</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.327281153</v>
+        <v>0.333965089</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180267812</v>
+        <v>0.179228636</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175069858</v>
+        <v>0.165608945</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203582769</v>
+        <v>0.189849288</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235955685</v>
+        <v>0.221300523</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255913518</v>
+        <v>0.245724669</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248655914</v>
+        <v>0.245527612</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6545,42 +6545,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>-0.010548257</v>
+        <v>-0.010587346</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010569797</v>
+        <v>-0.010577214</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010544605</v>
+        <v>-0.010543873</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010575201</v>
+        <v>-0.010577887</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010596168</v>
+        <v>-0.010581445</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010545906</v>
+        <v>-0.01057817</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010553039</v>
+        <v>-0.010563733</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010548237</v>
+        <v>-0.01057574</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010567581</v>
+        <v>-0.010553411</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010557258</v>
+        <v>-0.010574521</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.005126805</v>
+        <v>-0.0055264</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.009948557</v>
+        <v>-0.000148752</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.005824802</v>
+        <v>-0.00421926</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.258325847</v>
+        <v>1.259302856</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005343076</v>
+        <v>-0.005694309</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.003725885</v>
+        <v>-0.006625448</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001491692</v>
+        <v>0.001326312</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257767884</v>
+        <v>1.257788296</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006674811</v>
+        <v>0.006877652</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.004310413</v>
+        <v>-0.003736072</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.002057053</v>
+        <v>-0.008533024</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002262182</v>
+        <v>-0.002384434</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003704736</v>
+        <v>0.003741849</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.257668353</v>
+        <v>1.248753166</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004590109</v>
+        <v>0.005084632</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004692155</v>
+        <v>-0.004994323</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.004192485</v>
+        <v>-0.006034895</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.263376485</v>
+        <v>1.263413634</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004747262</v>
+        <v>0.00489335</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.004863878</v>
+        <v>-0.004453051</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7834,36 +7834,36 @@
         <v/>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.004199886</v>
+        <v>0.00401495</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.003130755</v>
+        <v>0.003131332</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.002753809</v>
+        <v>0.002570694</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.022153057</v>
+        <v>-0.022344322</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>-0.000936154</v>
+        <v>-0.00093668</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>-0.002248876</v>
+        <v>-0.002062629</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>-0.003756574</v>
+        <v>-0.003570086</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031485671</v>
+        <v>-0.031303036</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.011485303</v>
+        <v>-0.01109597</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.013391099</v>
+        <v>-0.013188976</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7962,36 +7962,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.002344092</v>
+        <v>0.002241055</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.001747533</v>
+        <v>0.001747713</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.001539251</v>
+        <v>0.001436782</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.012397541</v>
+        <v>-0.012502562</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.000518726</v>
+        <v>-0.000518888</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.001245589</v>
+        <v>-0.001142145</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.00207857</v>
+        <v>-0.001975052</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.01739221</v>
+        <v>-0.017289866</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006253312</v>
+        <v>-0.006041335</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.00725256</v>
+        <v>-0.00714438</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1549295774647887</v>
+        <v>0.1641791044776119</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471490135448181</v>
+        <v>0.1471553497942387</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.9863945578231292</v>
+        <v>0.986013986013986</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07447481591712297</v>
+        <v>0.07448342373273627</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18887,7 +18887,7 @@
         <v>-20.06</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V64" s="18" t="n">
         <v>-1.58</v>
@@ -18964,7 +18964,7 @@
         <v>-20.06</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V65" s="18" t="n">
         <v>-1.58</v>
@@ -33454,7 +33454,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="30">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>691.49</v>
+        <v>738.64</v>
       </c>
     </row>
     <row r="32">
@@ -33494,7 +33494,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3250</v>
+        <v>3255</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6241,29 +6241,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.520039769</v>
+        <v>0.5202208659999999</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.333965089</v>
+        <v>0.334113621</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179228636</v>
+        <v>0.179480716</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165608945</v>
+        <v>0.165911151</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189849288</v>
+        <v>0.190005361</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221300523</v>
+        <v>0.221498553</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245724669</v>
+        <v>0.245725582</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245527612</v>
+        <v>0.245463971</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6555,32 +6555,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010543873</v>
+        <v>-0.010542617</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010577887</v>
+        <v>-0.010576709</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010581445</v>
+        <v>-0.010579184</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.01057817</v>
+        <v>-0.010575428</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010563733</v>
+        <v>-0.010561089</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.01057574</v>
+        <v>-0.010572848</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010553411</v>
+        <v>-0.010551147</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010574521</v>
+        <v>-0.01057232</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.0055264</v>
+        <v>-0.005511141</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000148752</v>
+        <v>-0.000133459</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.00421926</v>
+        <v>-0.004203946</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259302856</v>
+        <v>1.259318246</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005694309</v>
+        <v>-0.005676273</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006625448</v>
+        <v>0.003392692</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001326312</v>
+        <v>-0.008655533999999999</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257788296</v>
+        <v>1.257806402</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006877652</v>
+        <v>0.006895582</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003736072</v>
+        <v>-0.003904579</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.008533024</v>
+        <v>-0.008517979</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002384434</v>
+        <v>-0.002369354</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003741849</v>
+        <v>0.003756948</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.248753166</v>
+        <v>1.258768341</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005084632</v>
+        <v>-0.004897584</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004994323</v>
+        <v>-0.004976436</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006034895</v>
+        <v>0.003983005</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.263413634</v>
+        <v>1.253431487</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00489335</v>
+        <v>0.004911028</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.004453051</v>
+        <v>0.0053808</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7860,10 +7860,10 @@
         <v>-0.031303036</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.01109597</v>
+        <v>-0.011290637</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.013188976</v>
+        <v>-0.012994684</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7988,10 +7988,10 @@
         <v>-0.017289866</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006041335</v>
+        <v>-0.006147324</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.00714438</v>
+        <v>-0.007038498</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3250</v>
+        <v>3255</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,270원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471553497942387</v>
+        <v>0.1471501897816226</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07448342373273627</v>
+        <v>0.07448417616083117</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>-20.06</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V64" s="18" t="n">
         <v>-1.58</v>
@@ -18964,7 +18964,7 @@
         <v>-20.06</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V65" s="18" t="n">
         <v>-1.58</v>
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>738.64</v>
+        <v>739.77</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6241,29 +6241,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.5202208659999999</v>
+        <v>0.520130318</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.334113621</v>
+        <v>0.334039355</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179480716</v>
+        <v>0.179354676</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165911151</v>
+        <v>0.165790269</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.190005361</v>
+        <v>0.189957112</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221498553</v>
+        <v>0.221399544</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245725582</v>
+        <v>0.245751844</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245463971</v>
+        <v>0.245489423</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6555,32 +6555,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010542617</v>
+        <v>-0.010543245</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010576709</v>
+        <v>-0.010577298</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010579184</v>
+        <v>-0.010580314</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010575428</v>
+        <v>-0.010576524</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010561089</v>
+        <v>-0.010562146</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010572848</v>
+        <v>-0.010574294</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010551147</v>
+        <v>-0.010552053</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.01057232</v>
+        <v>-0.010573201</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7457,29 +7457,29 @@
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.004203946</v>
+        <v>-0.004203949</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259318246</v>
+        <v>1.259318218</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005676273</v>
+        <v>-0.005676158</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.003392692</v>
+        <v>-0.006607196</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.008655533999999999</v>
+        <v>0.00134453</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257806402</v>
+        <v>1.257806335</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006895582</v>
+        <v>0.006895388</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003904579</v>
+        <v>-0.003904776</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7585,29 +7585,29 @@
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003756948</v>
+        <v>0.003756945</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.258768341</v>
+        <v>1.248768313</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004897584</v>
+        <v>0.00510253</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004976436</v>
+        <v>-0.004976327</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003983005</v>
+        <v>0.003983069</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.253431487</v>
+        <v>1.253431421</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004911028</v>
+        <v>0.004910837</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.0053808</v>
+        <v>0.005380606</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471501897816226</v>
+        <v>0.1471512557929009</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3255</v>
+        <v>3170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3283</v>
+        <v>3264.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3255</v>
+        <v>3170</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>739.77</v>
+        <v>720.45</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>· 지배주주 비중 98.6% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
+          <t>· 지배주주 비중 99.3% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3170</v>
+        <v>3075</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5991,7 +5991,7 @@
         <v>2505</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3100</v>
+        <v>3020</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3264.2</v>
+        <v>3235</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6237,33 +6237,33 @@
         <v>0.276330141</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.287368306</v>
+        <v>0.287290496</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.520130318</v>
+        <v>0.519858672</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.334039355</v>
+        <v>0.333593759</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179354676</v>
+        <v>0.178850517</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165790269</v>
+        <v>0.165195841</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189957112</v>
+        <v>0.189514447</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221399544</v>
+        <v>0.221250766</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245751844</v>
+        <v>0.245696568</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245489423</v>
+        <v>0.245681382</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6548,39 +6548,39 @@
         <v>-0.010587346</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010577214</v>
+        <v>-0.010577853</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010543245</v>
+        <v>-0.01054513</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010577298</v>
+        <v>-0.010580832</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010580314</v>
+        <v>-0.010584839</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010576524</v>
+        <v>-0.01058256</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010562146</v>
+        <v>-0.010567966</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010574294</v>
+        <v>-0.010579115</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010552053</v>
+        <v>-0.010557034</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010573201</v>
+        <v>-0.010577604</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.005511141</v>
+        <v>-0.005542153</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000133459</v>
+        <v>-0.000164493</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.004203949</v>
+        <v>-0.004235168</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259318218</v>
+        <v>1.259287069</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005676158</v>
+        <v>-0.005526811</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006607196</v>
+        <v>-0.006644156</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.00134453</v>
+        <v>0.00130757</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257806335</v>
+        <v>1.257769816</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006895388</v>
+        <v>-0.003140627</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003904776</v>
+        <v>-0.003754387</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.008517979</v>
+        <v>-0.007066677</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002369354</v>
+        <v>-0.001298078</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003756945</v>
+        <v>0.004731039</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.248768313</v>
+        <v>1.249008437</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.00510253</v>
+        <v>-0.005133004</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004976327</v>
+        <v>0.004183108</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003983069</v>
+        <v>-0.007354186</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.253431421</v>
+        <v>1.260622513</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004910837</v>
+        <v>-0.0090758</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.005380606</v>
+        <v>0.00095309</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7844,10 +7844,10 @@
         <v>0.002570694</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.022344322</v>
+        <v>-0.022161172</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>-0.00093668</v>
+        <v>-0.001123806</v>
       </c>
       <c r="AI32" s="24" t="n">
         <v>-0.002062629</v>
@@ -7857,13 +7857,13 @@
         <v>-0.003570086</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031303036</v>
+        <v>-0.031114464</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.011290637</v>
+        <v>-0.011288439</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.012994684</v>
+        <v>-0.012992126</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7972,10 +7972,10 @@
         <v>0.001436782</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.012502562</v>
+        <v>-0.012400082</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.000518888</v>
+        <v>-0.0006226</v>
       </c>
       <c r="AI33" s="24" t="n">
         <v>-0.001142145</v>
@@ -7988,10 +7988,10 @@
         <v>-0.017289866</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006147324</v>
+        <v>-0.006041335</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.007038498</v>
+        <v>-0.007037748</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3170</v>
+        <v>3075</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471512557929009</v>
+        <v>0.1471535595941301</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.986013986013986</v>
+        <v>0.9929078014184396</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07448417616083117</v>
+        <v>0.07448264695606233</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>720.45</v>
+        <v>698.86</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4105,14 +4105,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>· 판관비율 14.72% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
+          <t>· 판관비율 14.71% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>· 지배주주 비중 99.3% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
+          <t>· 지배주주 비중 98.6% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3075</v>
+        <v>3065</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3235</v>
+        <v>3216.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6241,29 +6241,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.519858672</v>
+        <v>0.520039769</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.333593759</v>
+        <v>0.333965089</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.178850517</v>
+        <v>0.179291656</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165195841</v>
+        <v>0.16580029</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189514447</v>
+        <v>0.189908858</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221250766</v>
+        <v>0.221356196</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245696568</v>
+        <v>0.245711537</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245681382</v>
+        <v>0.245450303</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6555,32 +6555,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.01054513</v>
+        <v>-0.010543873</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010580832</v>
+        <v>-0.010577887</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.010584839</v>
+        <v>-0.01058088</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.01058256</v>
+        <v>-0.010577073</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010567966</v>
+        <v>-0.010563204</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010579115</v>
+        <v>-0.010575258</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010557034</v>
+        <v>-0.010552958</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010577604</v>
+        <v>-0.010574081</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.005542153</v>
+        <v>-0.005511141</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000164493</v>
+        <v>-0.000133412</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.004235168</v>
+        <v>-0.004203941</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259287069</v>
+        <v>1.259318199</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005526811</v>
+        <v>-0.00567627</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006644156</v>
+        <v>-0.006607317</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.00130757</v>
+        <v>0.001344439</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257769816</v>
+        <v>1.257806339</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.003140627</v>
+        <v>0.006895467</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003754387</v>
+        <v>-0.003904697</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.007066677</v>
+        <v>-0.008517979</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.001298078</v>
+        <v>-0.002369308</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.004731039</v>
+        <v>0.003756954</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.249008437</v>
+        <v>1.248768294</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005133004</v>
+        <v>0.005102419</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.004183108</v>
+        <v>-0.004976445</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.007354186</v>
+        <v>0.003982977</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.260622513</v>
+        <v>1.253431426</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.0090758</v>
+        <v>0.004910915</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.00095309</v>
+        <v>-0.004619316</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7844,10 +7844,10 @@
         <v>0.002570694</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.022161172</v>
+        <v>-0.022344322</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>-0.001123806</v>
+        <v>-0.00093668</v>
       </c>
       <c r="AI32" s="24" t="n">
         <v>-0.002062629</v>
@@ -7857,13 +7857,13 @@
         <v>-0.003570086</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031114464</v>
+        <v>-0.031303036</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.011288439</v>
+        <v>-0.01109597</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.012992126</v>
+        <v>-0.013188976</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7972,10 +7972,10 @@
         <v>0.001436782</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.012400082</v>
+        <v>-0.012502562</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.0006226</v>
+        <v>-0.000518888</v>
       </c>
       <c r="AI33" s="24" t="n">
         <v>-0.001142145</v>
@@ -7988,10 +7988,10 @@
         <v>-0.017289866</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006041335</v>
+        <v>-0.006147324</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.007037748</v>
+        <v>-0.007038498</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3075</v>
+        <v>3065</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,270원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,150원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471535595941301</v>
+        <v>0.1471456642284703</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.9929078014184396</v>
+        <v>0.986013986013986</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07448264695606233</v>
+        <v>0.07448417616083117</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>698.86</v>
+        <v>696.59</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>· 지배주주 비중 98.6% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
+          <t>· 지배주주 비중 97.9% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3065</v>
+        <v>3085</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5991,7 +5991,7 @@
         <v>2505</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3020</v>
+        <v>2850</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3216.2</v>
+        <v>3165.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6237,33 +6237,33 @@
         <v>0.276330141</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.287290496</v>
+        <v>0.289080129</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.520039769</v>
+        <v>0.523480617</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.333965089</v>
+        <v>0.337009993</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179291656</v>
+        <v>0.181245274</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.16580029</v>
+        <v>0.163457476</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189908858</v>
+        <v>0.184249629</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221356196</v>
+        <v>0.214186524</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245711537</v>
+        <v>0.238583013</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245450303</v>
+        <v>0.241245136</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6548,39 +6548,39 @@
         <v>-0.010587346</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010577853</v>
+        <v>-0.010563168</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010543873</v>
+        <v>-0.010579495</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010577887</v>
+        <v>-0.010553797</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.01058088</v>
+        <v>-0.01056338</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010577073</v>
+        <v>-0.010583658</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010563204</v>
+        <v>-0.010589711</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.010575258</v>
+        <v>-0.01056773</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010552958</v>
+        <v>-0.010553067</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010574081</v>
+        <v>-0.010574713</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.005511141</v>
+        <v>-0.005494594</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000133412</v>
+        <v>-0.000116863</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.004203941</v>
+        <v>-0.002545598</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259318199</v>
+        <v>1.259334827</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.00567627</v>
+        <v>-0.005656488</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006607317</v>
+        <v>0.003226107</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001344439</v>
+        <v>-0.00882207</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257806339</v>
+        <v>1.257639713</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006895467</v>
+        <v>0.006914717</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003904697</v>
+        <v>-0.003513231</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.008517979</v>
+        <v>-0.010101853</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002369308</v>
+        <v>-0.00354293</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.003756954</v>
+        <v>-0.005491049</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.248768294</v>
+        <v>1.258491937</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005102419</v>
+        <v>0.005536152</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004976445</v>
+        <v>-0.004271596</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003982977</v>
+        <v>-0.004775882</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.253431426</v>
+        <v>1.266047433</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004910915</v>
+        <v>0.00898083</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.004619316</v>
+        <v>0.0004906240000000001</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7847,23 +7847,23 @@
         <v>-0.022344322</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>-0.00093668</v>
+        <v>-0.001124016</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>-0.002062629</v>
+        <v>-0.002063016</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>-0.003570086</v>
+        <v>-0.003570757</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031303036</v>
+        <v>-0.031120332</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.01109597</v>
+        <v>-0.010901304</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.013188976</v>
+        <v>-0.012792757</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -7975,23 +7975,23 @@
         <v>-0.012502562</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.000518888</v>
+        <v>-0.000622665</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.001142145</v>
+        <v>-0.001142264</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.001975052</v>
+        <v>-0.001975257</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.017289866</v>
+        <v>-0.0171875</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.006147324</v>
+        <v>-0.005935347</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.007038498</v>
+        <v>-0.006930376</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3065</v>
+        <v>3085</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,925원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471456642284703</v>
+        <v>0.1471471162213514</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.986013986013986</v>
+        <v>0.9785714285714288</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07448417616083117</v>
+        <v>0.07448499211484905</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>696.59</v>
+        <v>701.14</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100660_model.xlsx
+++ b/argus/kship/models/100660_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255852억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265700억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 274541억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 284424억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297400억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 313630억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 331909억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 350749억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 368148억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255852억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265700억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 274541억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 284424억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297400억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 313630억 × 비례계수 0.0026 × 계절비중 Q1 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 331909억 × 비례계수 0.0026 × 계절비중 Q2 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 350749억 × 비례계수 0.0026 × 계절비중 Q3 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 368148억 × 비례계수 0.0026 × 계절비중 Q4 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3970,7 +3970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4098,21 +4098,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 16.42% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 15.50% · 근거: 최근 12분기 유효세율 15.5%(5~27% 안 — 그대로)</t>
+          <t>· 세율 16.92% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 15.50% · 근거: 최근 12분기 유효세율 15.5%(5~27% 안 — 그대로)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>· 판관비율 14.71% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
+          <t>· 판관비율 14.72% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>· 지배주주 비중 97.9% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
+          <t>· 지배주주 비중 99.3% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
         </is>
       </c>
     </row>
@@ -4841,35 +4841,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4960,35 +4960,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5079,35 +5079,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5198,35 +5198,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5317,35 +5317,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5436,35 +5436,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5555,35 +5555,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5674,35 +5674,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5809,7 +5809,7 @@
         <v>3155</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3085</v>
+        <v>2950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6082,7 +6082,7 @@
         <v>3024.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3165.5</v>
+        <v>3113.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6237,33 +6237,33 @@
         <v>0.276330141</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.289080129</v>
+        <v>0.290480711</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.523480617</v>
+        <v>0.526468721</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.337009993</v>
+        <v>0.3398321</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.181245274</v>
+        <v>0.183324931</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163457476</v>
+        <v>0.162435936</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.184249629</v>
+        <v>0.180389133</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.214186524</v>
+        <v>0.208913031</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.238583013</v>
+        <v>0.233210843</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.241245136</v>
+        <v>0.237875408</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6548,39 +6548,39 @@
         <v>-0.010587346</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.010563168</v>
+        <v>-0.010551703</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.010579495</v>
+        <v>-0.010558785</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.010553797</v>
+        <v>-0.010586996</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.01056338</v>
+        <v>-0.010544815</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.010583658</v>
+        <v>-0.010581462</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.010589711</v>
+        <v>-0.010553294</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.01056773</v>
+        <v>-0.010591472</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.010553067</v>
+        <v>-0.010580411</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.010574713</v>
+        <v>-0.010559397</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7450,36 +7450,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.005494594</v>
+        <v>-0.006684409</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000116863</v>
+        <v>-0.000973193</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002545598</v>
+        <v>-0.003420922</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>1.259334827</v>
+        <v>1.260745052</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005656488</v>
+        <v>-0.005711613</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.003226107</v>
+        <v>0.003170885</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.00882207</v>
+        <v>0.000936258</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>1.257639713</v>
+        <v>1.257584118</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006914717</v>
+        <v>-0.012956889</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.003513231</v>
+        <v>0.00661433</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7578,36 +7578,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.010101853</v>
+        <v>-0.008233796999999999</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.00354293</v>
+        <v>-0.002125561</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.005491049</v>
+        <v>0.005589374</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>1.258491937</v>
+        <v>1.250522262</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005536152</v>
+        <v>0.004692094</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004271596</v>
+        <v>-0.005982527</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.004775882</v>
+        <v>0.002233821</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>1.266047433</v>
+        <v>1.250427711</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00898083</v>
+        <v>0.001122509</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.0004906240000000001</v>
+        <v>-0.008723455</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7837,27 +7837,27 @@
         <v>0.00401495</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.003131332</v>
+        <v>0.002947136</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.002570694</v>
+        <v>0.002571166</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.022344322</v>
+        <v>-0.022348415</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>-0.001124016</v>
+        <v>-0.001124227</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>-0.002063016</v>
+        <v>-0.002063403</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>-0.003570757</v>
+        <v>-0.003571429</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.031120332</v>
+        <v>-0.030937559</v>
       </c>
       <c r="AM32" s="24" t="n">
         <v>-0.010901304</v>
@@ -7965,27 +7965,27 @@
         <v>0.002241055</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.001747713</v>
+        <v>0.001644906</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.001436782</v>
+        <v>0.001436929</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.012502562</v>
+        <v>-0.012503843</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.000622665</v>
+        <v>-0.00062273</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.001142264</v>
+        <v>-0.001246235</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.001975257</v>
+        <v>-0.001871686</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.0171875</v>
+        <v>-0.017085113</v>
       </c>
       <c r="AM33" s="24" t="n">
         <v>-0.005935347</v>
@@ -8654,11 +8654,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3085</v>
+        <v>2950</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,925원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,975원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1641791044776119</v>
+        <v>0.1692307692307692</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1471471162213514</v>
+        <v>0.1471530560735147</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.9785714285714288</v>
+        <v>0.992753623188406</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07448499211484905</v>
+        <v>0.07449043280492576</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33474,7 +33474,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>701.14</v>
+        <v>670.45</v>
       </c>
     </row>
     <row r="32">
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="33">
